--- a/plantillas/eleccion/Mesas_Computadas.xlsx
+++ b/plantillas/eleccion/Mesas_Computadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\eleccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6BE0994-3078-4601-B6DD-043028B9D8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A434ABFD-A85E-4660-AA13-764B6F230066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3013CAC1-338C-4DC6-AF80-73336DC2E636}"/>
   </bookViews>
@@ -141,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -149,14 +149,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -492,58 +495,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{460B38C7-5B1D-4EA9-A160-A4B559021C91}">
-  <dimension ref="A2:E11"/>
+  <dimension ref="A2:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="1" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-    </row>
-    <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="D8" s="2" t="s">
+    <row r="2" spans="1:6" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D9" s="2" t="s">
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E9" s="2"/>
+      <c r="F9" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/plantillas/eleccion/Mesas_Computadas.xlsx
+++ b/plantillas/eleccion/Mesas_Computadas.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A434ABFD-A85E-4660-AA13-764B6F230066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3013CAC1-338C-4DC6-AF80-73336DC2E636}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3013CAC1-338C-4DC6-AF80-73336DC2E636}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
